--- a/release_1_0_0/data/files/input/v1_pilot_defaults.xlsx
+++ b/release_1_0_0/data/files/input/v1_pilot_defaults.xlsx
@@ -615,7 +615,7 @@
         <v>2.6</v>
       </c>
       <c r="P3" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>6669.74</v>
@@ -672,7 +672,7 @@
         <v>2.6</v>
       </c>
       <c r="P4" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
         <v>12558.375</v>
